--- a/doc/calculator_test_spec.xlsx
+++ b/doc/calculator_test_spec.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">テスト項目!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">テスト項目!$A$1:$J$75</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">テスト項目!$A$1:$J$93</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="479">
   <si>
     <t xml:space="preserve">電卓アプリ テスト仕様書兼結果表</t>
   </si>
@@ -87,7 +87,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0e1d16d </t>
+      <t xml:space="preserve">16554e3 </t>
     </r>
     <r>
       <rPr>
@@ -192,6 +192,40 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">、消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込計算・税率設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">、キーボード操作</t>
     </r>
   </si>
@@ -704,7 +738,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">のボタンが表示される。履歴欄に「履歴はありません」と表示される</t>
+      <t xml:space="preserve">のボタンと、「⚙ 設定」「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」のボタンが表示される。履歴欄に「履歴はありません」と表示される</t>
     </r>
   </si>
   <si>
@@ -748,7 +799,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">個、履歴欄「履歴はありません」</t>
+      <t xml:space="preserve">個</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+⚙ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定・消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、履歴欄「履歴はありません」</t>
     </r>
   </si>
   <si>
@@ -1412,7 +1497,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">19</t>
+      <t xml:space="preserve">21</t>
     </r>
     <r>
       <rPr>
@@ -1429,7 +1514,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">56px</t>
+      <t xml:space="preserve">44px</t>
     </r>
   </si>
   <si>
@@ -5884,6 +5969,2823 @@
     <t xml:space="preserve">T045</t>
   </si>
   <si>
+    <t xml:space="preserve">消費税・設定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税率の初期値</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初めて開いた状態</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定を変更していない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で消費税ボタンを確認する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボタンに「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」と表示される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待 「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T046</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消費税の計算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押した後、「消費税」ボタンを押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」。式の欄に「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」と表示される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、式欄「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">式に対する消費税</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 + 2 0 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押した後、「消費税」ボタンを押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">式が先に計算され、結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">((100+200)×1.1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、式欄「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100+200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計算結果に対する消費税</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 + 2 0 0 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の後、「消費税」ボタンを押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、式欄「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">端数が出る消費税</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押した後、「消費税」ボタンを押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誤差が出ず、丸められない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、式欄「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">105 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数値がない状態での消費税</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何も入力していない状態で「消費税」ボタンを押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">税込金額に続けて計算</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押して「消費税」、続けて </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 1 0 =</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(110 + 10)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待 「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税の履歴</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">履歴に「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%) =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">110</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」が追加される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">履歴 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">["100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%) =110"]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定画面を開く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「⚙ 設定」ボタンを押す</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面が表示され、消費税率の入力欄に現在の値「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」が入っている</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面の表示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、税率欄「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税率の変更</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」にして「保存」を押す。その後 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押して「消費税」ボタンを押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面が閉じ、ボタンが「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」になる。結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面を閉じた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小数の消費税率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」にして保存し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に「消費税」ボタン</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボタンが「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」になり、結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T056</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消費税率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」にして保存し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 0 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に「消費税」ボタン</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">結果が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待 「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全角数字での入力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を全角「８」「．」「５」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">８．５</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と入力して保存</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">半角と同様に扱われ、ボタンが「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」になる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期待 「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8.5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定のキャンセル</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に書き換えて「キャンセル」を押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面が閉じ、税率は変更されない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボタンは「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」のまま</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面を閉じた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T059</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定の保持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再読み込み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に変更して保存し、ページを再読み込みする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボタンが「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」のまま。設定画面にも「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」が表示される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再読み込み後 ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、設定画面の税率「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">税率の入力チェック</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空欄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">abc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」にして、それぞれ「保存」を押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">いずれも「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の数値を入力してください」と表示され、保存されず、設定画面は開いたまま</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パターン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空欄・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">abc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">101)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で、エラー表示・設定画面が開いたまま・税率不変とならなかったもの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">なし</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T061</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Enter / Esc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">での操作</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設定画面で税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」にして </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キー。再度設定画面を開き、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Esc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キーを押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で保存されて閉じる。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Esc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で保存せずに閉じる。どちらも電卓の計算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">履歴の追加など</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は行われない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Enter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">画面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">closed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Esc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">画面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">closed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、履歴件数 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1→1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、表示「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定画面中のキー入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定画面を開いた状態で、キーボードの数字キーを押す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字は税率の入力欄だけに入り、電卓の表示欄は変わらない</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税率欄「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、電卓の表示「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">変わらない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T063</t>
+  </si>
+  <si>
     <t xml:space="preserve">エラー処理</t>
   </si>
   <si>
@@ -6006,7 +8908,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T046</t>
+    <t xml:space="preserve">T064</t>
   </si>
   <si>
     <t xml:space="preserve">エラー後の復帰</t>
@@ -6137,7 +9039,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T047</t>
+    <t xml:space="preserve">T065</t>
   </si>
   <si>
     <t xml:space="preserve">エラーの履歴</t>
@@ -6168,7 +9070,7 @@
     <t xml:space="preserve">履歴「履歴はありません」</t>
   </si>
   <si>
-    <t xml:space="preserve">T048</t>
+    <t xml:space="preserve">T066</t>
   </si>
   <si>
     <t xml:space="preserve">履歴</t>
@@ -6240,7 +9142,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T049</t>
+    <t xml:space="preserve">T067</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の並び順</t>
@@ -6362,7 +9264,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T050</t>
+    <t xml:space="preserve">T068</t>
   </si>
   <si>
     <t xml:space="preserve">履歴からの再利用</t>
@@ -6435,7 +9337,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T051</t>
+    <t xml:space="preserve">T069</t>
   </si>
   <si>
     <r>
@@ -6499,7 +9401,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T052</t>
+    <t xml:space="preserve">T070</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の消去</t>
@@ -6514,7 +9416,7 @@
     <t xml:space="preserve">消去後「履歴はありません」、再読み込み後「履歴はありません」</t>
   </si>
   <si>
-    <t xml:space="preserve">T053</t>
+    <t xml:space="preserve">T071</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の消去と表示欄</t>
@@ -6596,7 +9498,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T054</t>
+    <t xml:space="preserve">T072</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の上限</t>
@@ -6719,7 +9621,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T055</t>
+    <t xml:space="preserve">T073</t>
   </si>
   <si>
     <t xml:space="preserve">履歴が多いときの表示</t>
@@ -6834,7 +9736,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T056</t>
+    <t xml:space="preserve">T074</t>
   </si>
   <si>
     <t xml:space="preserve">連続計算の履歴</t>
@@ -6956,7 +9858,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T057</t>
+    <t xml:space="preserve">T075</t>
   </si>
   <si>
     <r>
@@ -7061,7 +9963,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T058</t>
+    <t xml:space="preserve">T076</t>
   </si>
   <si>
     <t xml:space="preserve">履歴のダウンロード</t>
@@ -7166,7 +10068,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T059</t>
+    <t xml:space="preserve">T077</t>
   </si>
   <si>
     <r>
@@ -7475,7 +10377,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T060</t>
+    <t xml:space="preserve">T078</t>
   </si>
   <si>
     <r>
@@ -7758,7 +10660,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T061</t>
+    <t xml:space="preserve">T079</t>
   </si>
   <si>
     <t xml:space="preserve">履歴消去後のダウンロードボタン</t>
@@ -7806,7 +10708,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T062</t>
+    <t xml:space="preserve">T080</t>
   </si>
   <si>
     <t xml:space="preserve">キーボード操作</t>
@@ -7939,7 +10841,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T063</t>
+    <t xml:space="preserve">T081</t>
   </si>
   <si>
     <t xml:space="preserve">演算子キー</t>
@@ -8025,7 +10927,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T064</t>
+    <t xml:space="preserve">T082</t>
   </si>
   <si>
     <t xml:space="preserve">割り算キー</t>
@@ -8190,7 +11092,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T065</t>
+    <t xml:space="preserve">T083</t>
   </si>
   <si>
     <r>
@@ -8266,7 +11168,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T066</t>
+    <t xml:space="preserve">T084</t>
   </si>
   <si>
     <r>
@@ -8323,7 +11225,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T067</t>
+    <t xml:space="preserve">T085</t>
   </si>
   <si>
     <t xml:space="preserve">Backspace</t>
@@ -8365,7 +11267,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T068</t>
+    <t xml:space="preserve">T086</t>
   </si>
   <si>
     <t xml:space="preserve">Esc / Delete</t>
@@ -8494,7 +11396,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T069</t>
+    <t xml:space="preserve">T087</t>
   </si>
   <si>
     <t xml:space="preserve">小数点とパーセント</t>
@@ -8527,7 +11429,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T070</t>
+    <t xml:space="preserve">T088</t>
   </si>
   <si>
     <t xml:space="preserve">動作環境</t>
@@ -8673,7 +11575,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T071</t>
+    <t xml:space="preserve">T089</t>
   </si>
   <si>
     <t xml:space="preserve">Edge</t>
@@ -8734,7 +11636,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T072</t>
+    <t xml:space="preserve">T090</t>
   </si>
   <si>
     <t xml:space="preserve">Safari / iPhone</t>
@@ -8865,7 +11767,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T073</t>
+    <t xml:space="preserve">T091</t>
   </si>
   <si>
     <t xml:space="preserve">Android Chrome</t>
@@ -8960,7 +11862,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T074</t>
+    <t xml:space="preserve">T092</t>
   </si>
   <si>
     <t xml:space="preserve">GitHub Pages</t>
@@ -9720,8 +12622,8 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTA(テスト項目!A2:A75)</f>
-        <v>74</v>
+        <f aca="false">COUNTA(テスト項目!A2:A93)</f>
+        <v>92</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9729,8 +12631,8 @@
         <v>17</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(テスト項目!G2:G75,"OK")</f>
-        <v>70</v>
+        <f aca="false">COUNTIF(テスト項目!G2:G93,"OK")</f>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9738,7 +12640,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(テスト項目!G2:G75,"NG")</f>
+        <f aca="false">COUNTIF(テスト項目!G2:G93,"NG")</f>
         <v>0</v>
       </c>
     </row>
@@ -9757,7 +12659,7 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">IF(B12=0,0,(B13+B14)/B12)</f>
-        <v>0.945945945945946</v>
+        <v>0.956521739130435</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9785,7 +12687,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -9832,7 +12734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
         <v>31</v>
       </c>
@@ -11152,17 +14054,17 @@
       </c>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
         <v>248</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>251</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -11212,7 +14114,7 @@
       </c>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
         <v>259</v>
       </c>
@@ -11247,19 +14149,19 @@
         <v>264</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="E49" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="F49" s="12" t="s">
         <v>268</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>17</v>
@@ -11277,7 +14179,7 @@
         <v>269</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>270</v>
@@ -11307,7 +14209,7 @@
         <v>274</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>275</v>
@@ -11316,10 +14218,10 @@
         <v>276</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>277</v>
+        <v>166</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>17</v>
@@ -11332,24 +14234,24 @@
       </c>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B52" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C52" s="12" t="s">
+      <c r="E52" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="F52" s="12" t="s">
         <v>281</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>17</v>
@@ -11362,24 +14264,24 @@
       </c>
       <c r="J52" s="12"/>
     </row>
-    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E53" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="F53" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>288</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>17</v>
@@ -11392,24 +14294,24 @@
       </c>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="12" t="s">
+      <c r="F54" s="12" t="s">
         <v>290</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>293</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>17</v>
@@ -11422,24 +14324,24 @@
       </c>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C55" s="12" t="s">
+      <c r="F55" s="12" t="s">
         <v>295</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>298</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>17</v>
@@ -11454,22 +14356,22 @@
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="E56" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="F56" s="12" t="s">
         <v>300</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>303</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>17</v>
@@ -11482,24 +14384,24 @@
       </c>
       <c r="J56" s="12"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="F57" s="12" t="s">
         <v>305</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>308</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>17</v>
@@ -11514,22 +14416,22 @@
     </row>
     <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C58" s="12" t="s">
+      <c r="F58" s="12" t="s">
         <v>310</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>17</v>
@@ -11542,24 +14444,24 @@
       </c>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C59" s="12" t="s">
+      <c r="F59" s="12" t="s">
         <v>315</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>17</v>
@@ -11572,24 +14474,24 @@
       </c>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="B60" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C60" s="13" t="s">
+      <c r="F60" s="12" t="s">
         <v>320</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>323</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>17</v>
@@ -11604,22 +14506,22 @@
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E61" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C61" s="13" t="s">
+      <c r="F61" s="13" t="s">
         <v>325</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>328</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>17</v>
@@ -11632,24 +14534,24 @@
       </c>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C62" s="12" t="s">
+      <c r="F62" s="13" t="s">
         <v>330</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>333</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>17</v>
@@ -11662,24 +14564,24 @@
       </c>
       <c r="J62" s="12"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="F63" s="12" t="s">
         <v>335</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>339</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>17</v>
@@ -11694,22 +14596,22 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C64" s="12" t="s">
+      <c r="F64" s="12" t="s">
         <v>341</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>68</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>17</v>
@@ -11722,24 +14624,24 @@
       </c>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D65" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B65" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C65" s="12" t="s">
+      <c r="E65" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="F65" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>348</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>17</v>
@@ -11754,22 +14656,22 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="D66" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C66" s="12" t="s">
+      <c r="E66" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="F66" s="12" t="s">
         <v>351</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>107</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>17</v>
@@ -11784,22 +14686,22 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B67" s="12" t="s">
         <v>353</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>335</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="13" t="s">
         <v>355</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="G67" s="11" t="s">
         <v>17</v>
@@ -11814,22 +14716,22 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="D68" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>358</v>
       </c>
+      <c r="D68" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="E68" s="12" t="s">
-        <v>207</v>
+        <v>360</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>208</v>
+        <v>361</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>17</v>
@@ -11842,24 +14744,24 @@
       </c>
       <c r="J68" s="12"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>360</v>
+        <v>353</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>363</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>362</v>
+        <v>365</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>17</v>
@@ -11872,24 +14774,24 @@
       </c>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>238</v>
+        <v>370</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>127</v>
+        <v>371</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>17</v>
@@ -11904,22 +14806,22 @@
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>369</v>
+        <v>353</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>371</v>
+        <v>375</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>17</v>
@@ -11930,117 +14832,657 @@
       <c r="I71" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J71" s="13" t="s">
-        <v>372</v>
-      </c>
+      <c r="J71" s="12"/>
     </row>
-    <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>375</v>
+        <v>353</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>379</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H72" s="14"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="13" t="s">
-        <v>376</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J72" s="12"/>
     </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>378</v>
+        <v>353</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="F73" s="12"/>
-      <c r="G73" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H73" s="14"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="13" t="s">
-        <v>381</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J73" s="12"/>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>383</v>
+        <v>353</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="F74" s="12"/>
-      <c r="G74" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J74" s="12"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J77" s="12"/>
+    </row>
+    <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J78" s="12"/>
+    </row>
+    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J79" s="12"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J80" s="12"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J81" s="12"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J82" s="12"/>
+    </row>
+    <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J83" s="12"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J84" s="12"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J85" s="12"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J86" s="12"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J87" s="12"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J88" s="12"/>
+    </row>
+    <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H74" s="14"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="13" t="s">
-        <v>385</v>
+      <c r="H90" s="14"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="13" t="s">
+        <v>464</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="11" t="s">
-        <v>386</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="15" t="s">
+    <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="F91" s="12"/>
+      <c r="G91" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H75" s="14"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="12" t="s">
-        <v>390</v>
+      <c r="H91" s="14"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="13" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="F92" s="12"/>
+      <c r="G92" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="13" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="F93" s="12"/>
+      <c r="G93" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="14"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J75"/>
-  <conditionalFormatting sqref="G2:G75">
+  <autoFilter ref="A1:J93"/>
+  <conditionalFormatting sqref="G2:G93">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"OK"</formula>
     </cfRule>
@@ -12052,7 +15494,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G75" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G93" type="list">
       <formula1>"OK,NG,未実施"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/doc/calculator_test_spec.xlsx
+++ b/doc/calculator_test_spec.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">テスト項目!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">テスト項目!$A$1:$J$93</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">テスト項目!$A$1:$J$99</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="505">
   <si>
     <t xml:space="preserve">電卓アプリ テスト仕様書兼結果表</t>
   </si>
@@ -87,7 +87,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">16554e3 </t>
+      <t xml:space="preserve">4d617c7 </t>
     </r>
     <r>
       <rPr>
@@ -226,7 +226,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、キーボード操作</t>
+      <t xml:space="preserve">、オールクリア、キーボード操作</t>
     </r>
   </si>
   <si>
@@ -738,7 +738,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">のボタンと、「⚙ 設定」「消費税</t>
+      <t xml:space="preserve">のボタンと、「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「⚙ 設定」「消費税</t>
     </r>
     <r>
       <rPr>
@@ -808,15 +825,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+⚙ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">設定・消費税</t>
+      <t xml:space="preserve">+AC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・⚙ 設定・消費税</t>
     </r>
     <r>
       <rPr>
@@ -1497,7 +1514,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">21</t>
+      <t xml:space="preserve">22</t>
     </r>
     <r>
       <rPr>
@@ -5109,6 +5126,540 @@
     <t xml:space="preserve">T035</t>
   </si>
   <si>
+    <t xml:space="preserve">オールクリア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力途中でオールクリア</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 2 + 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押した後 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">表示が「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に戻り、式の欄も空になる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結果表示後にオールクリア</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 + 2 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の後 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オールクリアで履歴も消える</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計算を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回行い、履歴がある状態で </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押す。その後ページを再読み込みする</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">履歴が全て消え「履歴はありません」と表示される。「ダウンロード」ボタンは押せなくなる。再読み込みしても履歴は復活しない</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後の履歴「履歴はありません」、ダウンロード無効</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、再読み込み後「履歴はありません」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オールクリアで消費税率が初期値に戻る</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に変更して保存した後 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押す。その後ページを再読み込みする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消費税ボタンが「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に戻る。再読み込みしても「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」のまま</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、再読み込み後「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オールクリア後の再計算</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の後に </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 × 2 =</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T040</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">では履歴・税率は消えない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税率を「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に変更し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 + 2 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を実行した後 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を押す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">表示のみ「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」に戻り、履歴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1+2 =3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は残り、ボタンは「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」のまま</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">表示「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」、履歴件数 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -5124,6 +5675,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">、ボタン「消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">T041</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">文字削除</t>
     </r>
   </si>
@@ -5247,7 +5837,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T036</t>
+    <t xml:space="preserve">T042</t>
   </si>
   <si>
     <t xml:space="preserve">演算子の削除</t>
@@ -5325,7 +5915,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T037</t>
+    <t xml:space="preserve">T043</t>
   </si>
   <si>
     <t xml:space="preserve">小数点の削除</t>
@@ -5473,7 +6063,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T038</t>
+    <t xml:space="preserve">T044</t>
   </si>
   <si>
     <t xml:space="preserve">連続削除</t>
@@ -5542,7 +6132,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T039</t>
+    <t xml:space="preserve">T045</t>
   </si>
   <si>
     <t xml:space="preserve">空の状態で削除</t>
@@ -5604,7 +6194,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T040</t>
+    <t xml:space="preserve">T046</t>
   </si>
   <si>
     <t xml:space="preserve">削除後の計算</t>
@@ -5699,7 +6289,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T041</t>
+    <t xml:space="preserve">T047</t>
   </si>
   <si>
     <t xml:space="preserve">結果表示後の削除</t>
@@ -5751,7 +6341,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T042</t>
+    <t xml:space="preserve">T048</t>
   </si>
   <si>
     <t xml:space="preserve">パーセント</t>
@@ -5806,7 +6396,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T043</t>
+    <t xml:space="preserve">T049</t>
   </si>
   <si>
     <t xml:space="preserve">式の途中でのパーセント</t>
@@ -5938,7 +6528,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T044</t>
+    <t xml:space="preserve">T050</t>
   </si>
   <si>
     <t xml:space="preserve">数値がない状態</t>
@@ -5966,7 +6556,7 @@
     <t xml:space="preserve">何も起きない</t>
   </si>
   <si>
-    <t xml:space="preserve">T045</t>
+    <t xml:space="preserve">T051</t>
   </si>
   <si>
     <t xml:space="preserve">消費税・設定</t>
@@ -6116,7 +6706,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T046</t>
+    <t xml:space="preserve">T052</t>
   </si>
   <si>
     <r>
@@ -6347,7 +6937,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T047</t>
+    <t xml:space="preserve">T053</t>
   </si>
   <si>
     <t xml:space="preserve">式に対する消費税</t>
@@ -6520,7 +7110,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T048</t>
+    <t xml:space="preserve">T054</t>
   </si>
   <si>
     <t xml:space="preserve">計算結果に対する消費税</t>
@@ -6684,7 +7274,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T049</t>
+    <t xml:space="preserve">T055</t>
   </si>
   <si>
     <t xml:space="preserve">端数が出る消費税</t>
@@ -6874,7 +7464,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T050</t>
+    <t xml:space="preserve">T056</t>
   </si>
   <si>
     <t xml:space="preserve">数値がない状態での消費税</t>
@@ -6883,7 +7473,7 @@
     <t xml:space="preserve">何も入力していない状態で「消費税」ボタンを押す</t>
   </si>
   <si>
-    <t xml:space="preserve">T051</t>
+    <t xml:space="preserve">T057</t>
   </si>
   <si>
     <t xml:space="preserve">税込金額に続けて計算</t>
@@ -7023,7 +7613,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T052</t>
+    <t xml:space="preserve">T058</t>
   </si>
   <si>
     <t xml:space="preserve">消費税の履歴</t>
@@ -7126,7 +7716,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T053</t>
+    <t xml:space="preserve">T059</t>
   </si>
   <si>
     <t xml:space="preserve">設定画面を開く</t>
@@ -7206,7 +7796,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T054</t>
+    <t xml:space="preserve">T060</t>
   </si>
   <si>
     <t xml:space="preserve">消費税率の変更</t>
@@ -7378,7 +7968,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T055</t>
+    <t xml:space="preserve">T061</t>
   </si>
   <si>
     <t xml:space="preserve">小数の消費税率</t>
@@ -7533,7 +8123,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T056</t>
+    <t xml:space="preserve">T062</t>
   </si>
   <si>
     <r>
@@ -7696,7 +8286,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T057</t>
+    <t xml:space="preserve">T063</t>
   </si>
   <si>
     <t xml:space="preserve">全角数字での入力</t>
@@ -7843,7 +8433,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T058</t>
+    <t xml:space="preserve">T064</t>
   </si>
   <si>
     <t xml:space="preserve">設定のキャンセル</t>
@@ -7973,7 +8563,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T059</t>
+    <t xml:space="preserve">T065</t>
   </si>
   <si>
     <r>
@@ -8127,7 +8717,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T060</t>
+    <t xml:space="preserve">T066</t>
   </si>
   <si>
     <t xml:space="preserve">税率の入力チェック</t>
@@ -8376,7 +8966,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T061</t>
+    <t xml:space="preserve">T067</t>
   </si>
   <si>
     <r>
@@ -8701,7 +9291,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T062</t>
+    <t xml:space="preserve">T068</t>
   </si>
   <si>
     <t xml:space="preserve">設定画面中のキー入力</t>
@@ -8783,7 +9373,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T063</t>
+    <t xml:space="preserve">T069</t>
   </si>
   <si>
     <t xml:space="preserve">エラー処理</t>
@@ -8908,7 +9498,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T064</t>
+    <t xml:space="preserve">T070</t>
   </si>
   <si>
     <t xml:space="preserve">エラー後の復帰</t>
@@ -9039,7 +9629,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T065</t>
+    <t xml:space="preserve">T071</t>
   </si>
   <si>
     <t xml:space="preserve">エラーの履歴</t>
@@ -9070,7 +9660,7 @@
     <t xml:space="preserve">履歴「履歴はありません」</t>
   </si>
   <si>
-    <t xml:space="preserve">T066</t>
+    <t xml:space="preserve">T072</t>
   </si>
   <si>
     <t xml:space="preserve">履歴</t>
@@ -9142,7 +9732,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T067</t>
+    <t xml:space="preserve">T073</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の並び順</t>
@@ -9264,7 +9854,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T068</t>
+    <t xml:space="preserve">T074</t>
   </si>
   <si>
     <t xml:space="preserve">履歴からの再利用</t>
@@ -9337,7 +9927,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T069</t>
+    <t xml:space="preserve">T075</t>
   </si>
   <si>
     <r>
@@ -9401,7 +9991,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T070</t>
+    <t xml:space="preserve">T076</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の消去</t>
@@ -9416,7 +10006,7 @@
     <t xml:space="preserve">消去後「履歴はありません」、再読み込み後「履歴はありません」</t>
   </si>
   <si>
-    <t xml:space="preserve">T071</t>
+    <t xml:space="preserve">T077</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の消去と表示欄</t>
@@ -9498,7 +10088,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T072</t>
+    <t xml:space="preserve">T078</t>
   </si>
   <si>
     <t xml:space="preserve">履歴の上限</t>
@@ -9621,7 +10211,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T073</t>
+    <t xml:space="preserve">T079</t>
   </si>
   <si>
     <t xml:space="preserve">履歴が多いときの表示</t>
@@ -9736,7 +10326,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T074</t>
+    <t xml:space="preserve">T080</t>
   </si>
   <si>
     <t xml:space="preserve">連続計算の履歴</t>
@@ -9858,7 +10448,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T075</t>
+    <t xml:space="preserve">T081</t>
   </si>
   <si>
     <r>
@@ -9963,7 +10553,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T076</t>
+    <t xml:space="preserve">T082</t>
   </si>
   <si>
     <t xml:space="preserve">履歴のダウンロード</t>
@@ -10056,7 +10646,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">calculator-history_20261006.csv</t>
+      <t xml:space="preserve">calculator-history_20261024.csv</t>
     </r>
     <r>
       <rPr>
@@ -10068,7 +10658,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T077</t>
+    <t xml:space="preserve">T083</t>
   </si>
   <si>
     <r>
@@ -10377,7 +10967,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T078</t>
+    <t xml:space="preserve">T084</t>
   </si>
   <si>
     <r>
@@ -10660,7 +11250,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T079</t>
+    <t xml:space="preserve">T085</t>
   </si>
   <si>
     <t xml:space="preserve">履歴消去後のダウンロードボタン</t>
@@ -10708,7 +11298,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T080</t>
+    <t xml:space="preserve">T086</t>
   </si>
   <si>
     <t xml:space="preserve">キーボード操作</t>
@@ -10841,7 +11431,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T081</t>
+    <t xml:space="preserve">T087</t>
   </si>
   <si>
     <t xml:space="preserve">演算子キー</t>
@@ -10927,7 +11517,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T082</t>
+    <t xml:space="preserve">T088</t>
   </si>
   <si>
     <t xml:space="preserve">割り算キー</t>
@@ -11092,7 +11682,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T083</t>
+    <t xml:space="preserve">T089</t>
   </si>
   <si>
     <r>
@@ -11168,7 +11758,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T084</t>
+    <t xml:space="preserve">T090</t>
   </si>
   <si>
     <r>
@@ -11225,7 +11815,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T085</t>
+    <t xml:space="preserve">T091</t>
   </si>
   <si>
     <t xml:space="preserve">Backspace</t>
@@ -11267,7 +11857,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T086</t>
+    <t xml:space="preserve">T092</t>
   </si>
   <si>
     <t xml:space="preserve">Esc / Delete</t>
@@ -11396,7 +11986,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T087</t>
+    <t xml:space="preserve">T093</t>
   </si>
   <si>
     <t xml:space="preserve">小数点とパーセント</t>
@@ -11429,7 +12019,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T088</t>
+    <t xml:space="preserve">T094</t>
   </si>
   <si>
     <t xml:space="preserve">動作環境</t>
@@ -11575,7 +12165,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T089</t>
+    <t xml:space="preserve">T095</t>
   </si>
   <si>
     <t xml:space="preserve">Edge</t>
@@ -11636,7 +12226,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T090</t>
+    <t xml:space="preserve">T096</t>
   </si>
   <si>
     <t xml:space="preserve">Safari / iPhone</t>
@@ -11767,7 +12357,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T091</t>
+    <t xml:space="preserve">T097</t>
   </si>
   <si>
     <t xml:space="preserve">Android Chrome</t>
@@ -11862,7 +12452,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">T092</t>
+    <t xml:space="preserve">T098</t>
   </si>
   <si>
     <t xml:space="preserve">GitHub Pages</t>
@@ -12598,7 +13188,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12622,8 +13212,8 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTA(テスト項目!A2:A93)</f>
-        <v>92</v>
+        <f aca="false">COUNTA(テスト項目!A2:A99)</f>
+        <v>98</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12631,8 +13221,8 @@
         <v>17</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(テスト項目!G2:G93,"OK")</f>
-        <v>88</v>
+        <f aca="false">COUNTIF(テスト項目!G2:G99,"OK")</f>
+        <v>94</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12640,7 +13230,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(テスト項目!G2:G93,"NG")</f>
+        <f aca="false">COUNTIF(テスト項目!G2:G99,"NG")</f>
         <v>0</v>
       </c>
     </row>
@@ -12659,7 +13249,7 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">IF(B12=0,0,(B13+B14)/B12)</f>
-        <v>0.956521739130435</v>
+        <v>0.959183673469388</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12687,7 +13277,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -12757,7 +13347,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>37</v>
@@ -12787,7 +13377,7 @@
         <v>17</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>37</v>
@@ -12817,7 +13407,7 @@
         <v>17</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I4" s="13" t="s">
         <v>37</v>
@@ -12847,7 +13437,7 @@
         <v>17</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>37</v>
@@ -12877,7 +13467,7 @@
         <v>17</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>37</v>
@@ -12907,7 +13497,7 @@
         <v>17</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>37</v>
@@ -12937,7 +13527,7 @@
         <v>17</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>37</v>
@@ -12967,7 +13557,7 @@
         <v>17</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>37</v>
@@ -12997,7 +13587,7 @@
         <v>17</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>37</v>
@@ -13027,7 +13617,7 @@
         <v>17</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>37</v>
@@ -13057,7 +13647,7 @@
         <v>17</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>37</v>
@@ -13087,7 +13677,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>37</v>
@@ -13117,7 +13707,7 @@
         <v>17</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>37</v>
@@ -13147,7 +13737,7 @@
         <v>17</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>37</v>
@@ -13177,7 +13767,7 @@
         <v>17</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>37</v>
@@ -13207,7 +13797,7 @@
         <v>17</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>37</v>
@@ -13237,7 +13827,7 @@
         <v>17</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>37</v>
@@ -13267,7 +13857,7 @@
         <v>17</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>37</v>
@@ -13297,7 +13887,7 @@
         <v>17</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>37</v>
@@ -13327,7 +13917,7 @@
         <v>17</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>37</v>
@@ -13357,7 +13947,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>37</v>
@@ -13387,7 +13977,7 @@
         <v>17</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>37</v>
@@ -13417,7 +14007,7 @@
         <v>17</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>37</v>
@@ -13447,7 +14037,7 @@
         <v>17</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>37</v>
@@ -13477,7 +14067,7 @@
         <v>17</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>37</v>
@@ -13507,7 +14097,7 @@
         <v>17</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>37</v>
@@ -13537,7 +14127,7 @@
         <v>17</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I28" s="13" t="s">
         <v>37</v>
@@ -13567,7 +14157,7 @@
         <v>17</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>37</v>
@@ -13597,7 +14187,7 @@
         <v>17</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>37</v>
@@ -13627,7 +14217,7 @@
         <v>17</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>37</v>
@@ -13657,7 +14247,7 @@
         <v>17</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I32" s="13" t="s">
         <v>37</v>
@@ -13687,7 +14277,7 @@
         <v>17</v>
       </c>
       <c r="H33" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>37</v>
@@ -13717,7 +14307,7 @@
         <v>17</v>
       </c>
       <c r="H34" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I34" s="13" t="s">
         <v>37</v>
@@ -13747,7 +14337,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>37</v>
@@ -13758,7 +14348,7 @@
       <c r="A36" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>204</v>
       </c>
       <c r="C36" s="12" t="s">
@@ -13771,13 +14361,13 @@
         <v>207</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I36" s="13" t="s">
         <v>37</v>
@@ -13786,88 +14376,88 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>211</v>
-      </c>
       <c r="E37" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C38" s="12" t="s">
+      <c r="E38" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="F38" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>217</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H38" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I38" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="E39" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="F39" s="13" t="s">
         <v>220</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>37</v>
@@ -13876,58 +14466,58 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>224</v>
-      </c>
       <c r="E40" s="12" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I40" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J40" s="12"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C41" s="12" t="s">
+      <c r="E41" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="F41" s="12" t="s">
         <v>228</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>157</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>37</v>
@@ -13936,10 +14526,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B42" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>231</v>
@@ -13951,13 +14541,13 @@
         <v>233</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>37</v>
@@ -13966,10 +14556,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B43" s="12" t="s">
         <v>235</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>236</v>
@@ -13981,13 +14571,13 @@
         <v>238</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>37</v>
@@ -13998,8 +14588,8 @@
       <c r="A44" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>235</v>
+      <c r="B44" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>240</v>
@@ -14007,7 +14597,7 @@
       <c r="D44" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="12" t="s">
         <v>242</v>
       </c>
       <c r="F44" s="12" t="s">
@@ -14017,7 +14607,7 @@
         <v>17</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I44" s="13" t="s">
         <v>37</v>
@@ -14028,13 +14618,13 @@
       <c r="A45" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>235</v>
+      <c r="B45" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>246</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -14047,37 +14637,37 @@
         <v>17</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="D46" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="E46" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="E46" s="12" t="s">
-        <v>252</v>
-      </c>
       <c r="F46" s="12" t="s">
-        <v>253</v>
+        <v>147</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I46" s="13" t="s">
         <v>37</v>
@@ -14086,58 +14676,58 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C47" s="12" t="s">
+      <c r="E47" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>257</v>
-      </c>
       <c r="F47" s="12" t="s">
-        <v>258</v>
+        <v>157</v>
       </c>
       <c r="G47" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="B48" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>262</v>
-      </c>
       <c r="F48" s="12" t="s">
-        <v>263</v>
+        <v>147</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H48" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I48" s="13" t="s">
         <v>37</v>
@@ -14146,28 +14736,28 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>267</v>
-      </c>
       <c r="F49" s="12" t="s">
-        <v>268</v>
+        <v>127</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>37</v>
@@ -14176,88 +14766,88 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="F50" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>273</v>
       </c>
       <c r="G50" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H50" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I50" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J50" s="12"/>
     </row>
-    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>166</v>
+        <v>273</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J51" s="12"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="B52" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C52" s="12" t="s">
+      <c r="E52" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="F52" s="12" t="s">
         <v>279</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>281</v>
       </c>
       <c r="G52" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I52" s="13" t="s">
         <v>37</v>
@@ -14266,28 +14856,28 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D53" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="E53" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E53" s="12" t="s">
+      <c r="F53" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>285</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>37</v>
@@ -14296,88 +14886,88 @@
     </row>
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="E54" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="F54" s="12" t="s">
         <v>289</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>290</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I54" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C55" s="12" t="s">
+      <c r="D55" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="E55" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="F55" s="12" t="s">
         <v>294</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>295</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J55" s="12"/>
     </row>
-    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="D56" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="E56" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="F56" s="12" t="s">
         <v>299</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>300</v>
       </c>
       <c r="G56" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I56" s="13" t="s">
         <v>37</v>
@@ -14386,88 +14976,88 @@
     </row>
     <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="D57" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="D57" s="12" t="s">
-        <v>303</v>
-      </c>
       <c r="E57" s="12" t="s">
-        <v>304</v>
+        <v>166</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>305</v>
+        <v>167</v>
       </c>
       <c r="G57" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J57" s="12"/>
     </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C58" s="12" t="s">
+      <c r="F58" s="12" t="s">
         <v>307</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>310</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H58" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J58" s="12"/>
     </row>
-    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F59" s="12" t="s">
         <v>311</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>315</v>
       </c>
       <c r="G59" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>37</v>
@@ -14476,28 +15066,28 @@
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F60" s="12" t="s">
         <v>316</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="G60" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H60" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I60" s="13" t="s">
         <v>37</v>
@@ -14506,58 +15096,58 @@
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F61" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>325</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H61" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>326</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>330</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H62" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I62" s="13" t="s">
         <v>37</v>
@@ -14566,178 +15156,178 @@
     </row>
     <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="F63" s="12" t="s">
         <v>331</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>335</v>
       </c>
       <c r="G63" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H63" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>336</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>341</v>
       </c>
       <c r="G64" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H64" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I64" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J64" s="12"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>337</v>
+        <v>275</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>344</v>
+        <v>338</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>339</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H65" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J65" s="12"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>337</v>
+        <v>275</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>349</v>
+        <v>343</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H66" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I66" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J66" s="12"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>355</v>
+        <v>348</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>349</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>202</v>
+        <v>350</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>351</v>
       </c>
       <c r="G67" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H67" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B68" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>361</v>
+      <c r="D68" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>356</v>
       </c>
       <c r="G68" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I68" s="13" t="s">
         <v>37</v>
@@ -14746,88 +15336,88 @@
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="F70" s="12" t="s">
         <v>367</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>371</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H70" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I70" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="F71" s="12" t="s">
         <v>372</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>376</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H71" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>37</v>
@@ -14836,28 +15426,28 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="F72" s="12" t="s">
         <v>377</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>381</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H72" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I72" s="13" t="s">
         <v>37</v>
@@ -14866,88 +15456,88 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="E73" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="B73" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>386</v>
+      <c r="F73" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="G73" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H73" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J73" s="12"/>
     </row>
-    <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F74" s="12" t="s">
         <v>387</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>391</v>
       </c>
       <c r="G74" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H74" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I74" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J74" s="12"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>392</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>396</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H75" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>37</v>
@@ -14956,148 +15546,148 @@
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="F76" s="12" t="s">
         <v>397</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>401</v>
       </c>
       <c r="G76" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H76" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I76" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J76" s="12"/>
     </row>
-    <row r="77" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="F77" s="12" t="s">
         <v>402</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>406</v>
       </c>
       <c r="G77" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H77" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J77" s="12"/>
     </row>
-    <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="F78" s="12" t="s">
         <v>407</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>411</v>
       </c>
       <c r="G78" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H78" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I78" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J78" s="12"/>
     </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="F79" s="13" t="s">
         <v>412</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>416</v>
       </c>
       <c r="G79" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H79" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J79" s="12"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>421</v>
       </c>
       <c r="G80" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H80" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I80" s="13" t="s">
         <v>37</v>
@@ -15106,148 +15696,148 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="F81" s="12" t="s">
         <v>422</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>427</v>
       </c>
       <c r="G81" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H81" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J81" s="12"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="11" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>423</v>
+        <v>379</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>68</v>
+        <v>427</v>
       </c>
       <c r="G82" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H82" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I82" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J82" s="12"/>
     </row>
-    <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="F83" s="12" t="s">
         <v>432</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>436</v>
       </c>
       <c r="G83" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H83" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J83" s="12"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F84" s="13" t="s">
         <v>437</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>107</v>
       </c>
       <c r="G84" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H84" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I84" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J84" s="12"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="E85" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="B85" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C85" s="12" t="s">
+      <c r="F85" s="12" t="s">
         <v>442</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>58</v>
       </c>
       <c r="G85" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H85" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>37</v>
@@ -15256,28 +15846,28 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C86" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C86" s="13" t="s">
+      <c r="D86" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="E86" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="E86" s="12" t="s">
-        <v>207</v>
-      </c>
       <c r="F86" s="12" t="s">
-        <v>208</v>
+        <v>447</v>
       </c>
       <c r="G86" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H86" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I86" s="13" t="s">
         <v>37</v>
@@ -15286,28 +15876,28 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>450</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>450</v>
+        <v>452</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>453</v>
       </c>
       <c r="G87" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H87" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>37</v>
@@ -15316,28 +15906,28 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>238</v>
+        <v>457</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="G88" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H88" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I88" s="13" t="s">
         <v>37</v>
@@ -15346,143 +15936,323 @@
     </row>
     <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="11" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>457</v>
+        <v>449</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>460</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>459</v>
+        <v>461</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>462</v>
       </c>
       <c r="G89" s="11" t="s">
         <v>17</v>
       </c>
       <c r="H89" s="14" t="n">
-        <v>46301</v>
+        <v>46319</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J89" s="13" t="s">
-        <v>460</v>
-      </c>
+      <c r="J89" s="12"/>
     </row>
-    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>463</v>
+        <v>449</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>465</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="F90" s="12"/>
-      <c r="G90" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H90" s="14"/>
-      <c r="I90" s="12"/>
-      <c r="J90" s="13" t="s">
-        <v>464</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="14" t="n">
+        <v>46319</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J90" s="12"/>
     </row>
-    <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>467</v>
+        <v>449</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>469</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="F91" s="12"/>
-      <c r="G91" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H91" s="14"/>
-      <c r="I91" s="12"/>
-      <c r="J91" s="13" t="s">
-        <v>469</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>46319</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J91" s="12"/>
     </row>
-    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="s">
         <v>470</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>471</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="12" t="s">
         <v>472</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="F92" s="12"/>
-      <c r="G92" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>46319</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J92" s="12"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>46319</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J93" s="12"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>46319</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J94" s="12"/>
+    </row>
+    <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>46319</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F96" s="12"/>
+      <c r="G96" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H92" s="14"/>
-      <c r="I92" s="12"/>
-      <c r="J92" s="13" t="s">
-        <v>473</v>
+      <c r="H96" s="14"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="13" t="s">
+        <v>490</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="G93" s="15" t="s">
+    <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="F97" s="12"/>
+      <c r="G97" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H93" s="14"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12" t="s">
-        <v>478</v>
+      <c r="H97" s="14"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="13" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F98" s="12"/>
+      <c r="G98" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" s="14"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="13" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="F99" s="12"/>
+      <c r="G99" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" s="14"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
-  <conditionalFormatting sqref="G2:G93">
+  <autoFilter ref="A1:J99"/>
+  <conditionalFormatting sqref="G2:G99">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"OK"</formula>
     </cfRule>
@@ -15494,7 +16264,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G93" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G99" type="list">
       <formula1>"OK,NG,未実施"</formula1>
       <formula2>0</formula2>
     </dataValidation>
